--- a/manufacturing_forms/003_product_sample_reorder_request_form--manufacturing_forms.xlsx
+++ b/manufacturing_forms/003_product_sample_reorder_request_form--manufacturing_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'select_a_product',_'value':_1}</t>
+          <t>select_a_product</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Select a product', 'value': 1}</t>
+          <t>Select a product</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'select_a_different_product',_'value':_2}</t>
+          <t>select_a_different_product</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Select a different product', 'value': 2}</t>
+          <t>Select a different product</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'select_another_product',_'value':_3}</t>
+          <t>select_another_product</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Select another product', 'value': 3}</t>
+          <t>Select another product</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'standard',_'value':_'standard'}</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Standard', 'value': 'Standard'}</t>
+          <t>Standard</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'express',_'value':_'express'}</t>
+          <t>express</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Express', 'value': 'Express'}</t>
+          <t>Express</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'premium',_'value':_'premium'}</t>
+          <t>premium</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Premium', 'value': 'Premium'}</t>
+          <t>Premium</t>
         </is>
       </c>
     </row>
